--- a/ns-3.45/result_csv/cu_0125_RSSI_main_Load10.xlsx
+++ b/ns-3.45/result_csv/cu_0125_RSSI_main_Load10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamikawa/Desktop/ns-allinone-3.45/ns-3.45/result_csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10777BCC-5904-684B-A5F3-77F6D99AC777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF0D05E-72DE-174E-AB91-2E74207868E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5560" yWindow="1220" windowWidth="27900" windowHeight="16180" xr2:uid="{71A8D72E-9A5D-944F-BCDD-89CA964AB4A8}"/>
+    <workbookView xWindow="940" yWindow="2200" windowWidth="27900" windowHeight="16180" xr2:uid="{71A8D72E-9A5D-944F-BCDD-89CA964AB4A8}"/>
   </bookViews>
   <sheets>
     <sheet name="本実験データ_Load10" sheetId="1" r:id="rId1"/>
@@ -798,1038 +798,6 @@
           </c:spPr>
           <c:xVal>
             <c:numRef>
-              <c:f>本実験データ_Load10!$S$2:$S$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>-31.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-52.646799999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-61.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-66.960400000000007</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-70.708600000000004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-73.615899999999996</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-75.991299999999995</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$I$2:$I$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>17.889199999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>17.9147</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>19.872900000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>17.896699999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>20.2636</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>22.315200000000001</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>31.885899999999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000012-6FA6-CB45-A067-87DC1FF6F58D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="7"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>N=2</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="38100" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:xVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$S$2:$S$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>-31.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-52.646799999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-61.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-66.960400000000007</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-70.708600000000004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-73.615899999999996</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-75.991299999999995</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$I$9:$I$15</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>36.433300000000003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>36.3887</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>39.997</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>39.603400000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>44.071199999999997</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>39.831800000000001</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>44.216200000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000015-6FA6-CB45-A067-87DC1FF6F58D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>N=3</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="38100" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:xVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$S$16:$S$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>-31.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-52.646799999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-61.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-66.960400000000007</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-70.708600000000004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-73.615899999999996</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-75.991299999999995</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$I$16:$I$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>50.244999999999997</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>50.172400000000003</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>52.968899999999998</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>52.821100000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>57.281199999999998</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>59.849899999999998</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>50.0944</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000013-6FA6-CB45-A067-87DC1FF6F58D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:v>N=4</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="38100" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:xVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$S$16:$S$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>-31.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-52.646799999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-61.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-66.960400000000007</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-70.708600000000004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-73.615899999999996</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-75.991299999999995</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$I$23:$I$29</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>55.020499999999998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>55.6295</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>58.6845</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>61.366500000000002</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>66.278899999999993</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>63.508000000000003</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>61.006100000000004</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000D-6FA6-CB45-A067-87DC1FF6F58D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:v>N=5</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="38100" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$S$2:$S$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>-31.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-52.646799999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-61.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-66.960400000000007</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-70.708600000000004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-73.615899999999996</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-75.991299999999995</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$I$30:$I$36</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>61.0396</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>62.106400000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>65.084699999999998</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>67.062799999999996</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>70.448599999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>74.495599999999996</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>65.202600000000004</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000011-6FA6-CB45-A067-87DC1FF6F58D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:v>N=6</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="38100">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:xVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$S$2:$S$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>-31.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-52.646799999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-61.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-66.960400000000007</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-70.708600000000004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-73.615899999999996</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-75.991299999999995</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$I$37:$I$43</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>67.587900000000005</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>66.675299999999993</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>70.144300000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>69.915099999999995</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>72.5852</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>70.757499999999993</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>66.596500000000006</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000F-6FA6-CB45-A067-87DC1FF6F58D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="6"/>
-          <c:tx>
-            <c:v>N=7</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="38100">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:xVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$S$2:$S$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>-31.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-52.646799999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-61.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-66.960400000000007</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-70.708600000000004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-73.615899999999996</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-75.991299999999995</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$I$44:$I$50</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>74.835499999999996</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>72.613799999999998</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>72.060500000000005</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>74.753900000000002</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>79.240700000000004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>75.531999999999996</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>77.958699999999993</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000B-6FA6-CB45-A067-87DC1FF6F58D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="6"/>
-          <c:order val="7"/>
-          <c:tx>
-            <c:v>N=8</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="38100">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:xVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$S$51:$S$57</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>-31.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-52.646799999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-61.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-66.960400000000007</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-70.708600000000004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-73.615899999999996</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-75.991299999999995</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$I$51:$I$57</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>73.108699999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>75.134699999999995</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>74.957999999999998</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>75.824399999999997</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>82.105099999999993</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>83.999200000000002</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>72.272999999999996</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000014-6FA6-CB45-A067-87DC1FF6F58D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="8"/>
-          <c:order val="8"/>
-          <c:tx>
-            <c:v>N=9</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="38100">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:xVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$S$58:$S$64</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>-31.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-52.646799999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-61.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-66.960400000000007</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-70.708600000000004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-73.615899999999996</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-75.991299999999995</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$I$58:$I$64</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>79.368899999999996</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>82.078900000000004</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>78.982299999999995</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>79.978099999999998</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>85.013199999999998</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>82.062399999999997</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>75.641800000000003</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0895-B047-87D7-F238F5ED605A}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="9"/>
-          <c:order val="9"/>
-          <c:tx>
-            <c:v>N=10</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="38100">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:xVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$S$65:$S$71</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>-31.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-52.646799999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-61.677700000000002</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-66.960400000000007</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-70.708600000000004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-73.615899999999996</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-75.991299999999995</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>本実験データ_Load10!$I$65:$I$71</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>82.222800000000007</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>79.644900000000007</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>79.452699999999993</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>81.409300000000002</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>85.6648</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>87.747799999999998</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>79.426699999999997</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0895-B047-87D7-F238F5ED605A}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1016676799"/>
-        <c:axId val="1016680383"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1016676799"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" vert="horz"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>RSSI(dBm)</a:t>
-                </a:r>
-                <a:endParaRPr lang="ja-JP"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" vert="horz"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:endParaRPr lang="ja-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1016680383"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1016680383"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" vert="horz"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ja-JP"/>
-                  <a:t>チャネル使用率</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" altLang="ja-JP"/>
-                  <a:t>(%)</a:t>
-                </a:r>
-                <a:endParaRPr lang="ja-JP"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" vert="horz"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:endParaRPr lang="ja-JP"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1016676799"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="0"/>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst/>
-  </c:chart>
-  <c:spPr>
-    <a:ln>
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="25000"/>
-          <a:lumOff val="75000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </a:ln>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr sz="1800"/>
-      </a:pPr>
-      <a:endParaRPr lang="ja-JP"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ja-JP"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>N=1</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="38100">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:xVal>
-            <c:numRef>
               <c:f>本実験データ_Load10!$P$2:$P$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
@@ -2833,7 +1801,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ja-JP"/>
@@ -3875,44 +2843,1196 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>N=1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$S$2:$S$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$I$2:$I$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>17.889199999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17.9147</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19.872900000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17.896699999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20.2636</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>22.315200000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>31.885899999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-99F8-C947-91B0-572A5D419237}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>N=2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$S$2:$S$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$I$9:$I$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>36.433300000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36.3887</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39.997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39.603400000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>44.071199999999997</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>39.831800000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>44.216200000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-99F8-C947-91B0-572A5D419237}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>N=3</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$S$16:$S$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$I$16:$I$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>50.244999999999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>50.172400000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>52.968899999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>52.821100000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>57.281199999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>59.849899999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50.0944</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-99F8-C947-91B0-572A5D419237}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>N=4</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$S$16:$S$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$I$23:$I$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>55.020499999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>55.6295</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>58.6845</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>61.366500000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>66.278899999999993</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>63.508000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>61.006100000000004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-99F8-C947-91B0-572A5D419237}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>N=5</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$S$2:$S$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$I$30:$I$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>61.0396</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>62.106400000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>65.084699999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>67.062799999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>70.448599999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>74.495599999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>65.202600000000004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-99F8-C947-91B0-572A5D419237}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>N=6</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$S$2:$S$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$I$37:$I$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>67.587900000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>66.675299999999993</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>70.144300000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>69.915099999999995</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>72.5852</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>70.757499999999993</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>66.596500000000006</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-99F8-C947-91B0-572A5D419237}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:v>N=7</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$S$2:$S$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$I$44:$I$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>74.835499999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>72.613799999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>72.060500000000005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>74.753900000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>79.240700000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>75.531999999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>77.958699999999993</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-99F8-C947-91B0-572A5D419237}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:v>N=8</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$S$51:$S$57</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$I$51:$I$57</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>73.108699999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>75.134699999999995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>74.957999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>75.824399999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>82.105099999999993</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>83.999200000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>72.272999999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-99F8-C947-91B0-572A5D419237}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:v>N=9</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$S$58:$S$64</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$I$58:$I$64</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>79.368899999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>82.078900000000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>78.982299999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>79.978099999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>85.013199999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>82.062399999999997</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75.641800000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-99F8-C947-91B0-572A5D419237}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:v>N=10</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$S$65:$S$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$I$65:$I$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>82.222800000000007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>79.644900000000007</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>79.452699999999993</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>81.409300000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>85.6648</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>87.747799999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>79.426699999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-99F8-C947-91B0-572A5D419237}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:v>N=15</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$S$72:$S$78</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$I$72:$I$78</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>86.094399999999993</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85.634699999999995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>87.571600000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>87.124600000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>88.010099999999994</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>89.343999999999994</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>88.967699999999994</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000028-99F8-C947-91B0-572A5D419237}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:v>N=20</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$S$72:$S$78</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>-31.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52.646799999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-61.677700000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-66.960400000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-70.708600000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-73.615899999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-75.991299999999995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>本実験データ_Load10!$I$79:$I$85</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>87.118700000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>89.744799999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>88.560100000000006</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>86.474100000000007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>88.642600000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>90.130799999999994</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>88.359899999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000029-99F8-C947-91B0-572A5D419237}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1016676799"/>
+        <c:axId val="1016680383"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1016676799"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>RSSI(dBm)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1016680383"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1016680383"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ja-JP"/>
+                  <a:t>チャネル使用率</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ja-JP"/>
+                  <a:t>(%)</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" vert="horz"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1016676799"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1800"/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>564444</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>199383</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>631512</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>177</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="グラフ 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8C74DD7-310E-42EF-E5FF-229507AB6D93}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -3945,6 +4065,44 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>562506</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>3</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>376296</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>7440</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="グラフ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0222CEEC-A741-9949-BAA2-5B08155EFDA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
@@ -3953,23 +4111,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>515469</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>172471</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>768272</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>78395</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>329259</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>179908</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>835341</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>130053</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="グラフ 7">
+        <xdr:cNvPr id="2" name="グラフ 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0222CEEC-A741-9949-BAA2-5B08155EFDA2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86FB30E3-2F21-2346-AB42-E7BB635B94E3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
